--- a/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0003T0006Z000C1N79_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0003T0006Z000C1N79_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>55.04598269517118</v>
+        <v>8.944972187965316</v>
       </c>
       <c r="D2" t="n">
-        <v>54.9097789960235</v>
+        <v>8.92283908685382</v>
       </c>
       <c r="E2" t="n">
-        <v>16.73650159411788</v>
+        <v>2.719681509044155</v>
       </c>
       <c r="F2" t="n">
-        <v>15.94898696136702</v>
+        <v>2.591710381222141</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>32.93317448731842</v>
+        <v>5.351640854189244</v>
       </c>
       <c r="D3" t="n">
-        <v>32.88038587642834</v>
+        <v>5.343062704919606</v>
       </c>
       <c r="E3" t="n">
-        <v>16.73650159411788</v>
+        <v>2.719681509044155</v>
       </c>
       <c r="F3" t="n">
-        <v>15.94898696136702</v>
+        <v>2.591710381222141</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>32.83053423127392</v>
+        <v>5.334961812582013</v>
       </c>
       <c r="D4" t="n">
-        <v>34.61884848540909</v>
+        <v>5.625562878878977</v>
       </c>
       <c r="E4" t="n">
-        <v>16.73650159411788</v>
+        <v>2.719681509044155</v>
       </c>
       <c r="F4" t="n">
-        <v>15.94898696136702</v>
+        <v>2.591710381222141</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>10.65422887616728</v>
+        <v>1.731312192377183</v>
       </c>
       <c r="D5" t="n">
-        <v>15.45565534135383</v>
+        <v>2.511543992969998</v>
       </c>
       <c r="E5" t="n">
-        <v>16.73650159411788</v>
+        <v>2.719681509044155</v>
       </c>
       <c r="F5" t="n">
-        <v>15.94898696136702</v>
+        <v>2.591710381222141</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>45.3851986252612</v>
+        <v>7.375094776604945</v>
       </c>
       <c r="D6" t="n">
-        <v>45.91293307031379</v>
+        <v>7.460851623925992</v>
       </c>
       <c r="E6" t="n">
-        <v>16.73650159411788</v>
+        <v>2.719681509044155</v>
       </c>
       <c r="F6" t="n">
-        <v>15.94898696136702</v>
+        <v>2.591710381222141</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>22.01754790999612</v>
+        <v>3.57785153537437</v>
       </c>
       <c r="D7" t="n">
-        <v>20.91298007289098</v>
+        <v>3.398359261844785</v>
       </c>
       <c r="E7" t="n">
-        <v>16.73650159411788</v>
+        <v>2.719681509044155</v>
       </c>
       <c r="F7" t="n">
-        <v>15.94898696136702</v>
+        <v>2.591710381222141</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>11.35481658745819</v>
+        <v>1.845157695461956</v>
       </c>
       <c r="D8" t="n">
-        <v>11.31954140730637</v>
+        <v>1.839425478687285</v>
       </c>
       <c r="E8" t="n">
-        <v>16.73650159411788</v>
+        <v>2.719681509044155</v>
       </c>
       <c r="F8" t="n">
-        <v>15.94898696136702</v>
+        <v>2.591710381222141</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>5.919487064414839</v>
+        <v>0.9619166479674114</v>
       </c>
       <c r="D9" t="n">
-        <v>5.815227751913356</v>
+        <v>0.9449745096859203</v>
       </c>
       <c r="E9" t="n">
-        <v>16.73650159411788</v>
+        <v>2.719681509044155</v>
       </c>
       <c r="F9" t="n">
-        <v>15.94898696136702</v>
+        <v>2.591710381222141</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>51.66757916036776</v>
+        <v>8.39598161355976</v>
       </c>
       <c r="D10" t="n">
-        <v>48.17346119399955</v>
+        <v>7.828187444024927</v>
       </c>
       <c r="E10" t="n">
-        <v>16.73650159411788</v>
+        <v>2.719681509044155</v>
       </c>
       <c r="F10" t="n">
-        <v>15.94898696136702</v>
+        <v>2.591710381222141</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>39.53409232950912</v>
+        <v>6.424290003545233</v>
       </c>
       <c r="D11" t="n">
-        <v>39.55111064222461</v>
+        <v>6.427055479361499</v>
       </c>
       <c r="E11" t="n">
-        <v>16.73650159411788</v>
+        <v>2.719681509044155</v>
       </c>
       <c r="F11" t="n">
-        <v>15.94898696136702</v>
+        <v>2.591710381222141</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
